--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UEMC BALONCESTO VALLADOLID.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UEMC BALONCESTO VALLADOLID.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2798</v>
+        <v>4.3071</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4208</v>
+        <v>6.6281</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1411</v>
+        <v>-2.3209</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1567</v>
+        <v>3.1916</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9615</v>
+        <v>4.0103</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8048</v>
+        <v>-0.8186000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0082</v>
+        <v>6.166700000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>7.5307</v>
+        <v>7.6629</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.5225</v>
+        <v>-1.4962</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.8513</v>
+        <v>-2.9751</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.5691</v>
+        <v>-3.6527</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7178</v>
+        <v>0.6776</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6145</v>
+        <v>0.6073999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6387</v>
+        <v>1.6197</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09060000000000001</v>
+        <v>0.09510000000000007</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2563</v>
+        <v>0.2834</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1657</v>
+        <v>-0.1883</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4179</v>
+        <v>0.413</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7628</v>
+        <v>-0.7772</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.613</v>
+        <v>2.610300000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3868</v>
+        <v>2.5969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2262</v>
+        <v>0.01329999999999987</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.4485</v>
+        <v>-4.5025</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.7353</v>
+        <v>-3.7547</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.7478</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0904</v>
+        <v>-1.0117</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4726</v>
+        <v>-0.3991</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6178</v>
+        <v>-0.6126</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3581</v>
+        <v>-3.4908</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.2627</v>
+        <v>-3.3557</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.09549999999999999</v>
+        <v>-0.1352</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6387</v>
+        <v>1.6197</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2026</v>
+        <v>3.1702</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6749</v>
+        <v>1.6986</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5277</v>
+        <v>1.4716</v>
       </c>
       <c r="V3" t="n">
-        <v>4.4735</v>
+        <v>4.55</v>
       </c>
       <c r="W3" t="n">
-        <v>4.0556</v>
+        <v>4.137</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4179</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0383</v>
+        <v>2.0256</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1755</v>
+        <v>4.3542</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1371</v>
+        <v>-2.3285</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2735</v>
+        <v>-0.3067</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4875999999999999</v>
+        <v>0.475</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7610999999999999</v>
+        <v>-0.7817000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8676</v>
+        <v>1.9446</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3249</v>
+        <v>1.3808</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5427</v>
+        <v>0.5637999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1411</v>
+        <v>-2.2514</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.9058000000000002</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3038</v>
+        <v>-1.3456</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6146</v>
+        <v>0.6072999999999998</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0484</v>
+        <v>2.0246</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2747</v>
+        <v>0.2838</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4124</v>
+        <v>0.4424999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1377</v>
+        <v>-0.1588</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4226</v>
+        <v>1.4412</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3295</v>
+        <v>3.3841</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.9068</v>
+        <v>-1.943</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6529</v>
+        <v>1.6442</v>
       </c>
       <c r="E5" t="n">
-        <v>0.486</v>
+        <v>0.6526000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1668</v>
+        <v>0.9917</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3329</v>
+        <v>-1.3054</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2350999999999999</v>
+        <v>0.2936000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.568</v>
+        <v>-1.5988</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4177999999999999</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1001</v>
+        <v>1.2195</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6823</v>
+        <v>-0.6686000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7508</v>
+        <v>-1.8562</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.865</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8857999999999999</v>
+        <v>-0.9303</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.229</v>
+        <v>-1.2148</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9615</v>
+        <v>1.9373</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2972</v>
+        <v>1.3164</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6643</v>
+        <v>0.621</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,28 +877,28 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1709</v>
+        <v>1.1853</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7420000000000002</v>
+        <v>-0.7855000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8072999999999999</v>
+        <v>0.9889</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5493</v>
+        <v>-1.7744</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08530000000000015</v>
+        <v>0.03779999999999983</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5969999999999999</v>
+        <v>-0.6309</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6822000000000001</v>
+        <v>0.6686000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8398</v>
+        <v>1.9208</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6657</v>
+        <v>2.7248</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8258000000000001</v>
+        <v>-0.8040999999999998</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7546</v>
+        <v>-1.883</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.2626</v>
+        <v>-3.3557</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5081</v>
+        <v>1.4727</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4097</v>
+        <v>-0.4048999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4581</v>
+        <v>-2.4295</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S7" t="n">
         <v>-0.4872</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1776</v>
+        <v>-1.1338</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6905</v>
+        <v>0.6466000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0697000000000001</v>
+        <v>0.06879999999999997</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.5336</v>
+        <v>-2.5625</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.3056</v>
+        <v>-4.2421</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5163000000000002</v>
+        <v>-0.2755000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.7894</v>
+        <v>-3.9667</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.71</v>
+        <v>-0.6877</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7644</v>
+        <v>0.8081999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4745</v>
+        <v>-1.4959</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6065</v>
+        <v>2.7326</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1034</v>
+        <v>2.2086</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5032</v>
+        <v>0.5239999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3165</v>
+        <v>-3.4203</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3388</v>
+        <v>-1.4003</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9777</v>
+        <v>-2.0199</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0969</v>
+        <v>-4.0491</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.752</v>
+        <v>-1.7324</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.6291</v>
+        <v>-1.5905</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1229</v>
+        <v>-0.1419</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.6033</v>
+        <v>-2.6313</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.497199999999999</v>
+        <v>-4.4862</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8046</v>
+        <v>-3.7355</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6925999999999999</v>
+        <v>-0.7506999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4923</v>
+        <v>-3.5071</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2545</v>
+        <v>-1.2646</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2379</v>
+        <v>-2.2426</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5524</v>
+        <v>-2.531</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1983</v>
+        <v>-1.1867</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.354</v>
+        <v>-1.3444</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9760000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.07799999999999996</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8838</v>
+        <v>-0.8980999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.229</v>
+        <v>-1.2148</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6145</v>
+        <v>0.6073999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6324</v>
+        <v>-0.6226</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5073</v>
+        <v>-0.4916</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1251</v>
+        <v>-0.1311</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9704</v>
+        <v>-5.9958</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1087</v>
+        <v>-1.0169</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.861599999999999</v>
+        <v>-4.9789</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4083</v>
+        <v>-3.4115</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2687</v>
+        <v>-2.2542</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1396</v>
+        <v>-1.1572</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4843</v>
+        <v>-0.4373</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4843</v>
+        <v>-0.4373</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9241</v>
+        <v>-2.9741</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7844</v>
+        <v>-1.8169</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1396</v>
+        <v>-1.1572</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0484</v>
+        <v>-2.0246</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5943</v>
+        <v>1.5936</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8784</v>
+        <v>1.8822</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2841</v>
+        <v>-0.2887</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.5418</v>
+        <v>-3.5706</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4544</v>
+        <v>-0.4374</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.0874</v>
+        <v>-3.1332</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0749</v>
+        <v>-6.0803</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.499499999999999</v>
+        <v>-5.2476</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5754000000000001</v>
+        <v>-0.8329</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.1734</v>
+        <v>-5.1975</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.1835</v>
+        <v>-4.1715</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9898000000000001</v>
+        <v>-1.0261</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.2594</v>
+        <v>-3.1287</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3667</v>
+        <v>-1.2513</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8927</v>
+        <v>-1.8775</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.914</v>
+        <v>-2.0688</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.8169</v>
+        <v>-2.9203</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9029</v>
+        <v>0.8514</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.5309</v>
+        <v>-5.4662</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1016</v>
+        <v>2.0851</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6261</v>
+        <v>1.6553</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4753999999999999</v>
+        <v>0.4298</v>
       </c>
       <c r="V11" t="n">
-        <v>0.06959999999999997</v>
+        <v>0.06889999999999996</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6648</v>
+        <v>1.692</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5951</v>
+        <v>-1.6233</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8666</v>
+        <v>-6.8248</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9983</v>
+        <v>-3.6881</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8682</v>
+        <v>-3.1367</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.4459</v>
+        <v>-7.4624</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.8674</v>
+        <v>-5.870699999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5785</v>
+        <v>-1.5916</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.8775</v>
+        <v>-3.7289</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.1863</v>
+        <v>-2.081</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.6911</v>
+        <v>-1.648</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.5684</v>
+        <v>-3.7334</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.681</v>
+        <v>-3.789800000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1126000000000001</v>
+        <v>0.05630000000000002</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8193</v>
+        <v>0.8099000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R12" t="n">
-        <v>3.0727</v>
+        <v>3.0368</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7621</v>
+        <v>-1.7467</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9232</v>
+        <v>-1.8692</v>
       </c>
       <c r="U12" t="n">
-        <v>0.161</v>
+        <v>0.1224</v>
       </c>
       <c r="V12" t="n">
-        <v>1.522</v>
+        <v>1.5745</v>
       </c>
       <c r="W12" t="n">
-        <v>4.0556</v>
+        <v>4.1369</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.5337</v>
+        <v>-2.5625</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.7018</v>
+        <v>-16.6422</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5198999999999963</v>
+        <v>2.4424</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.2217</v>
+        <v>-19.0847</v>
       </c>
       <c r="G13" t="n">
-        <v>-21.8719</v>
+        <v>-21.9661</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.2869</v>
+        <v>-11.1742</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.5852</v>
+        <v>-10.7917</v>
       </c>
       <c r="J13" t="n">
-        <v>2.646800000000001</v>
+        <v>3.6633</v>
       </c>
       <c r="K13" t="n">
-        <v>10.1875</v>
+        <v>11.0265</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.540299999999999</v>
+        <v>-7.3636</v>
       </c>
       <c r="M13" t="n">
-        <v>-24.5189</v>
+        <v>-25.6291</v>
       </c>
       <c r="N13" t="n">
-        <v>-21.4737</v>
+        <v>-22.2011</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.044799999999999</v>
+        <v>-3.4283</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.0969</v>
+        <v>-4.0491</v>
       </c>
       <c r="Q13" t="n">
-        <v>-23.557</v>
+        <v>-23.2825</v>
       </c>
       <c r="R13" t="n">
-        <v>19.4602</v>
+        <v>19.2333</v>
       </c>
       <c r="S13" t="n">
-        <v>4.591600000000001</v>
+        <v>4.5762</v>
       </c>
       <c r="T13" t="n">
-        <v>1.908100000000001</v>
+        <v>2.1933</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6834</v>
+        <v>2.3826</v>
       </c>
       <c r="V13" t="n">
-        <v>4.6756</v>
+        <v>4.796700000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>19.5224</v>
+        <v>19.8673</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.8469</v>
+        <v>-15.0709</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UEMC BALONCESTO VALLADOLID.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UEMC BALONCESTO VALLADOLID.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3071</v>
+        <v>4.6541</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6281</v>
+        <v>6.548500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.3209</v>
+        <v>-1.8944</v>
       </c>
       <c r="G2" t="n">
         <v>3.1916</v>
@@ -610,13 +610,13 @@
         <v>1.6197</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09510000000000007</v>
+        <v>0.4421</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2834</v>
+        <v>0.2038</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1883</v>
+        <v>0.2382</v>
       </c>
       <c r="V2" t="n">
         <v>0.413</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. ORDONEZ OCHOA</t>
+          <t>J. HANNA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.610300000000001</v>
+        <v>2.6782</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5969</v>
+        <v>4.6899</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01329999999999987</v>
+        <v>-2.0116</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.5025</v>
+        <v>-0.3067</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.7547</v>
+        <v>0.475</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7478</v>
+        <v>-0.7817000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0117</v>
+        <v>1.9446</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3991</v>
+        <v>1.3808</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6126</v>
+        <v>0.5637999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.4908</v>
+        <v>-2.2514</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.3557</v>
+        <v>-0.9058000000000002</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1352</v>
+        <v>-1.3456</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6074000000000001</v>
+        <v>0.6072999999999998</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.227</v>
+        <v>-1.4172</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6197</v>
+        <v>2.0246</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1702</v>
+        <v>0.9364</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6986</v>
+        <v>0.7782</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4716</v>
+        <v>0.1582</v>
       </c>
       <c r="V3" t="n">
-        <v>4.55</v>
+        <v>1.4412</v>
       </c>
       <c r="W3" t="n">
-        <v>4.137</v>
+        <v>3.3841</v>
       </c>
       <c r="X3" t="n">
-        <v>0.413</v>
+        <v>-1.943</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HANNA</t>
+          <t>I. ORDONEZ OCHOA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0256</v>
+        <v>1.4636</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3542</v>
+        <v>1.8304</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3285</v>
+        <v>-0.3667999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3067</v>
+        <v>-4.5025</v>
       </c>
       <c r="H4" t="n">
-        <v>0.475</v>
+        <v>-3.7547</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7817000000000001</v>
+        <v>-0.7478</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9446</v>
+        <v>-1.0117</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3808</v>
+        <v>-0.3991</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5637999999999999</v>
+        <v>-0.6126</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2514</v>
+        <v>-3.4908</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9058000000000002</v>
+        <v>-3.3557</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3456</v>
+        <v>-0.1352</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6072999999999998</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4172</v>
+        <v>-2.227</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0246</v>
+        <v>1.6197</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2838</v>
+        <v>2.0236</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4424999999999999</v>
+        <v>0.9321</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1588</v>
+        <v>1.0914</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4412</v>
+        <v>4.55</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3841</v>
+        <v>4.137</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.943</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,61 +796,61 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6442</v>
+        <v>1.1853</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6526000000000001</v>
+        <v>1.1853</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9917</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3054</v>
+        <v>1.1853</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2936000000000001</v>
+        <v>1.1853</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5988</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5508999999999999</v>
+        <v>1.1853</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2195</v>
+        <v>1.1853</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6686000000000001</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8562</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9258999999999999</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9303</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0123</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2148</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.227</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9373</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3164</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.621</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,61 +874,61 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1853</v>
+        <v>0.5382999999999998</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1853</v>
+        <v>-0.04990000000000006</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1853</v>
+        <v>-1.3054</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1853</v>
+        <v>0.2936000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-1.5988</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1853</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1853</v>
+        <v>1.2195</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6686000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.8562</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.9303</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.0123</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.2148</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.227</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.8314999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.6139</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2176</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7855000000000001</v>
+        <v>0.3463000000000003</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9889</v>
+        <v>2.1551</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7744</v>
+        <v>-1.8089</v>
       </c>
       <c r="G7" t="n">
         <v>0.03779999999999983</v>
@@ -1000,13 +1000,13 @@
         <v>2.0245</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4872</v>
+        <v>0.6446</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1338</v>
+        <v>0.03239999999999998</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6466000000000001</v>
+        <v>0.6121000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0.06879999999999997</v>
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2421</v>
+        <v>-2.8056</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2755000000000001</v>
+        <v>0.9304999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.9667</v>
+        <v>-3.7361</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6877</v>
@@ -1078,13 +1078,13 @@
         <v>2.227</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7324</v>
+        <v>-0.2958999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5905</v>
+        <v>-0.3845</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1419</v>
+        <v>0.08860000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4862</v>
+        <v>-3.6378</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7355</v>
+        <v>-2.9447</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7506999999999999</v>
+        <v>-0.6931</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5071</v>
@@ -1156,13 +1156,13 @@
         <v>0.6073999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6226</v>
+        <v>0.2258</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4916</v>
+        <v>0.2992</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1311</v>
+        <v>-0.07340000000000002</v>
       </c>
       <c r="V9" t="n">
         <v>0.2509</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. TAIWO</t>
+          <t>I. HANEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9958</v>
+        <v>-5.1287</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0169</v>
+        <v>-2.2745</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.9789</v>
+        <v>-2.8542</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4115</v>
+        <v>-7.4624</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2542</v>
+        <v>-5.870699999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1572</v>
+        <v>-1.5916</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4373</v>
+        <v>-3.7289</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4373</v>
+        <v>-2.081</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.648</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9741</v>
+        <v>-3.7334</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8169</v>
+        <v>-3.789800000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1572</v>
+        <v>0.05630000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6074000000000001</v>
+        <v>0.8099000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0246</v>
+        <v>-2.227</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4172</v>
+        <v>3.0368</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5936</v>
+        <v>-0.05059999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8822</v>
+        <v>-0.4556</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2887</v>
+        <v>0.405</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.5706</v>
+        <v>1.5745</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4374</v>
+        <v>4.1369</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.1332</v>
+        <v>-2.5625</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>S. TAIWO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0803</v>
+        <v>-6.9411</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2476</v>
+        <v>-1.991</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8329</v>
+        <v>-4.9501</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.1975</v>
+        <v>-3.4115</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.1715</v>
+        <v>-2.2542</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0261</v>
+        <v>-1.1572</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.1287</v>
+        <v>-0.4373</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2513</v>
+        <v>-0.4373</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8775</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0688</v>
+        <v>-2.9741</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.9203</v>
+        <v>-1.8169</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8514</v>
+        <v>-1.1572</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.0368</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.4662</v>
+        <v>-2.0246</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4294</v>
+        <v>1.4172</v>
       </c>
       <c r="S11" t="n">
-        <v>2.0851</v>
+        <v>0.6483</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6553</v>
+        <v>0.9080999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4298</v>
+        <v>-0.2599</v>
       </c>
       <c r="V11" t="n">
-        <v>0.06889999999999996</v>
+        <v>-3.5706</v>
       </c>
       <c r="W11" t="n">
-        <v>1.692</v>
+        <v>-0.4374</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6233</v>
+        <v>-3.1332</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. HANEY</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8248</v>
+        <v>-7.3422</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6881</v>
+        <v>-6.6767</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1367</v>
+        <v>-0.6656</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.4624</v>
+        <v>-5.1975</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.870699999999999</v>
+        <v>-4.1715</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5916</v>
+        <v>-1.0261</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.7289</v>
+        <v>-3.1287</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.081</v>
+        <v>-1.2513</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.648</v>
+        <v>-1.8775</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.7334</v>
+        <v>-2.0688</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.789800000000001</v>
+        <v>-2.9203</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05630000000000002</v>
+        <v>0.8514</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8099000000000001</v>
+        <v>-3.0368</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.227</v>
+        <v>-5.4662</v>
       </c>
       <c r="R12" t="n">
-        <v>3.0368</v>
+        <v>2.4294</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7467</v>
+        <v>0.8233</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8692</v>
+        <v>0.2261</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1224</v>
+        <v>0.597</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5745</v>
+        <v>0.06889999999999996</v>
       </c>
       <c r="W12" t="n">
-        <v>4.1369</v>
+        <v>1.692</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.5625</v>
+        <v>-1.6233</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.6422</v>
+        <v>-14.9896</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4424</v>
+        <v>3.402900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-19.0847</v>
+        <v>-18.3926</v>
       </c>
       <c r="G13" t="n">
         <v>-21.9661</v>
@@ -1468,16 +1468,16 @@
         <v>19.2333</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5762</v>
+        <v>6.229099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1933</v>
+        <v>3.1537</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3826</v>
+        <v>3.0748</v>
       </c>
       <c r="V13" t="n">
-        <v>4.796700000000001</v>
+        <v>4.7967</v>
       </c>
       <c r="W13" t="n">
         <v>19.8673</v>
